--- a/example.xlsx
+++ b/example.xlsx
@@ -1,43 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\devops\openpyxl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B18E2F1-FB05-4A82-9F82-7E55C1F1C6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="NewSheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="score" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NewSheet" sheetId="1" r:id="rId1"/>
+    <sheet name="balance" sheetId="2" r:id="rId2"/>
+    <sheet name="score" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -56,88 +96,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -437,106 +418,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
         <v>2000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
         <v>4000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
         <v>5000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
         <v>6000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
         <v>7000</v>
       </c>
     </row>
@@ -547,93 +502,71 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
         <v>80</v>
       </c>
     </row>

--- a/example.xlsx
+++ b/example.xlsx
@@ -1,83 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\devops\openpyxl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B18E2F1-FB05-4A82-9F82-7E55C1F1C6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NewSheet" sheetId="1" r:id="rId1"/>
-    <sheet name="balance" sheetId="2" r:id="rId2"/>
-    <sheet name="score" sheetId="3" r:id="rId3"/>
+    <sheet name="NewSheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="score" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Balance</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -96,29 +56,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0"/>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -418,80 +437,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>3000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>4000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>7000</v>
       </c>
     </row>
@@ -502,71 +547,93 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>80</v>
       </c>
     </row>

--- a/example.xlsx
+++ b/example.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>Balance</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Double Balance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -479,6 +484,9 @@
       <c r="B2" s="1" t="n">
         <v>1000</v>
       </c>
+      <c r="C2" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -489,6 +497,9 @@
       <c r="B3" s="1" t="n">
         <v>2000</v>
       </c>
+      <c r="C3" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -499,6 +510,9 @@
       <c r="B4" s="1" t="n">
         <v>3000</v>
       </c>
+      <c r="C4" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -509,6 +523,9 @@
       <c r="B5" s="1" t="n">
         <v>4000</v>
       </c>
+      <c r="C5" t="n">
+        <v>8000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -519,6 +536,9 @@
       <c r="B6" s="1" t="n">
         <v>5000</v>
       </c>
+      <c r="C6" t="n">
+        <v>10000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -529,6 +549,9 @@
       <c r="B7" s="1" t="n">
         <v>6000</v>
       </c>
+      <c r="C7" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -537,7 +560,36 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>7000</v>
+        <v>7100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18000</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +686,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>80</v>
+        <v>7000</v>
       </c>
     </row>
   </sheetData>

--- a/example.xlsx
+++ b/example.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,19 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F30E0E"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -63,6 +76,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,6 +477,9 @@
   </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="14.109375" bestFit="1" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -469,7 +492,7 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Double Balance</t>
         </is>
@@ -484,7 +507,7 @@
       <c r="B2" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -497,7 +520,7 @@
       <c r="B3" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -510,7 +533,7 @@
       <c r="B4" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -523,7 +546,7 @@
       <c r="B5" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -536,7 +559,7 @@
       <c r="B6" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="5" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -549,7 +572,7 @@
       <c r="B7" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -562,7 +585,7 @@
       <c r="B8" s="1" t="n">
         <v>7100</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="5" t="n">
         <v>14200</v>
       </c>
     </row>
@@ -575,7 +598,7 @@
       <c r="B9" t="n">
         <v>8000</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>16000</v>
       </c>
     </row>
@@ -588,7 +611,7 @@
       <c r="B10" t="n">
         <v>9000</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="5" t="n">
         <v>18000</v>
       </c>
     </row>

--- a/example.xlsx
+++ b/example.xlsx
@@ -48,12 +48,17 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F30E0E"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -83,6 +88,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,7 +538,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="6" t="n">
         <v>3000</v>
       </c>
       <c r="C4" s="5" t="n">

--- a/example.xlsx
+++ b/example.xlsx
@@ -61,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -69,11 +69,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="dashed">
+        <color rgb="001818F9"/>
+      </top>
+    </border>
+    <border>
+      <top style="dashed">
+        <color rgb="001818F9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001FF918"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -89,6 +102,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -564,7 +583,7 @@
           <t>E</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="8" t="n">
         <v>5000</v>
       </c>
       <c r="C6" s="5" t="n">

--- a/example.xlsx
+++ b/example.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="NewSheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,8 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,15 +39,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00F30E0E"/>
+      <color rgb="FFF30E0E"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -57,11 +53,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F30E0E"/>
+        <fgColor rgb="FFF30E0E"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -70,23 +66,21 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="dashed">
-        <color rgb="001818F9"/>
-      </top>
-    </border>
-    <border>
-      <top style="dashed">
-        <color rgb="001818F9"/>
+        <color rgb="FF1818F9"/>
       </top>
       <bottom style="double">
-        <color rgb="001FF918"/>
+        <color rgb="FF1FF918"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -97,19 +91,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,7 +512,7 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Double Balance</t>
         </is>
@@ -534,7 +527,7 @@
       <c r="B2" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -547,7 +540,7 @@
       <c r="B3" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -557,10 +550,10 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -573,7 +566,7 @@
       <c r="B5" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -583,10 +576,10 @@
           <t>E</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -599,7 +592,7 @@
       <c r="B7" s="1" t="n">
         <v>6000</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -612,7 +605,7 @@
       <c r="B8" s="1" t="n">
         <v>7100</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>14200</v>
       </c>
     </row>
@@ -625,7 +618,7 @@
       <c r="B9" t="n">
         <v>8000</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>16000</v>
       </c>
     </row>
@@ -638,7 +631,7 @@
       <c r="B10" t="n">
         <v>9000</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>18000</v>
       </c>
     </row>
@@ -654,8 +647,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="13.44140625" customWidth="1" min="3" max="3"/>
+    <col width="12.6640625" customWidth="1" min="4" max="4"/>
+    <col width="13.109375" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -668,6 +666,22 @@
           <t>Score</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Multipier</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Skill Level</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -678,6 +692,19 @@
       <c r="B2" s="1" t="n">
         <v>20</v>
       </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>12/22/19</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Expert</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -688,6 +715,7 @@
       <c r="B3" s="1" t="n">
         <v>30</v>
       </c>
+      <c r="C3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -698,6 +726,19 @@
       <c r="B4" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>11/11/20</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -708,6 +749,7 @@
       <c r="B5" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="C5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -718,6 +760,7 @@
       <c r="B6" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="C6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -728,6 +771,7 @@
       <c r="B7" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="C7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -738,6 +782,7 @@
       <c r="B8" s="1" t="n">
         <v>7000</v>
       </c>
+      <c r="C8" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/example.xlsx
+++ b/example.xlsx
@@ -1,52 +1,156 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\devops\openpyxl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2884B777-9760-4C24-9142-1FA2D4C1C3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="NewSheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="score" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NewSheet" sheetId="1" r:id="rId1"/>
+    <sheet name="balance" sheetId="2" r:id="rId2"/>
+    <sheet name="score" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Double Balance</t>
+  </si>
+  <si>
+    <t>Interest RatE Per Yr</t>
+  </si>
+  <si>
+    <t>Total Balance After 1 Yr</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Multipier</t>
+  </si>
+  <si>
+    <t>Skill Level</t>
+  </si>
+  <si>
+    <t>12/22/19</t>
+  </si>
+  <si>
+    <t>Expert</t>
+  </si>
+  <si>
+    <t>11/11/20</t>
+  </si>
+  <si>
+    <t>Beginner</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFF30E0E"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFF30E0E"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -80,104 +184,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -477,162 +526,210 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="14.109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Double Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
         <v>1000</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="4">
         <v>2000</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
+      <c r="D2" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="E2">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
         <v>2000</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="4">
         <v>4000</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
+      <c r="D3" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="E3">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5">
         <v>3000</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4">
         <v>6000</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
+      <c r="D4" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="E4">
+        <v>6240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
         <v>4000</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>8000</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="D5" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="E5">
+        <v>8480</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6">
         <v>5000</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4">
         <v>10000</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
+      <c r="D6" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E6">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1">
         <v>6000</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>12000</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
+      <c r="D7" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="E7">
+        <v>12480</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
         <v>7100</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4">
         <v>14200</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="D8" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="E8">
+        <v>15336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>8000</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>16000</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="D9" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="E9">
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>9000</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>18000</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="E10">
+        <v>18180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B10)</f>
+        <v>45100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <f>AVERAGE(B2:B10)</f>
+        <v>5011.1111111111113</v>
       </c>
     </row>
   </sheetData>
@@ -642,147 +739,111 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="13.44140625" customWidth="1" min="3" max="3"/>
-    <col width="12.6640625" customWidth="1" min="4" max="4"/>
-    <col width="13.109375" customWidth="1" min="5" max="5"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Multipier</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Skill Level</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
         <v>20</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>12/22/19</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="n">
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8">
         <v>9</v>
       </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>Expert</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
+      <c r="E2" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
         <v>30</v>
       </c>
-      <c r="C3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1">
         <v>40</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>11/11/20</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n">
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="11">
         <v>20</v>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
+      <c r="E4" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
         <v>50</v>
       </c>
-      <c r="C5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
         <v>60</v>
       </c>
-      <c r="C6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1">
         <v>70</v>
       </c>
-      <c r="C7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
         <v>7000</v>
       </c>
-      <c r="C8" s="7" t="n"/>
+      <c r="C8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
